--- a/reports/pdf_rolling5_20260917.xlsx
+++ b/reports/pdf_rolling5_20260917.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,551억   ·   현금 68억(1.5%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 9종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,551억   ·   현금 34억(0.7%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 9종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -816,90 +816,90 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1262912230</v>
+        <v>-1122371766</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.70%</t>
+          <t>0.79%→0.47%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>137→98</t>
+          <t>112→73</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3457655789</v>
+        <v>853152692</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.09%→1.87%</t>
+          <t>1.62%→1.79%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>26→44</t>
+          <t>153→171</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1122371766</v>
+        <v>-1262912230</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.47%</t>
+          <t>1.09%→0.70%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>112→73</t>
+          <t>137→98</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>853152692</v>
+        <v>8432427875</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.62%→1.79%</t>
+          <t>4.74%→6.64%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>153→171</t>
+          <t>46→64</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>8432427875</v>
+        <v>3457655789</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>4.74%→6.64%</t>
+          <t>1.09%→1.87%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>46→64</t>
+          <t>26→44</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1092,23 +1092,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-773573155</v>
+        <v>-435435200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.13%→1.05%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>143→131</t>
         </is>
       </c>
     </row>
@@ -1120,23 +1120,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-435435200</v>
+        <v>-773573155</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.13%→1.05%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>143→131</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1204,23 +1204,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1222521862</v>
+        <v>-2189188006</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>6.50%→5.50%</t>
+          <t>3.36%→2.58%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>192→183</t>
+          <t>57→48</t>
         </is>
       </c>
     </row>
@@ -1232,23 +1232,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2189188006</v>
+        <v>-1222521862</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.36%→2.58%</t>
+          <t>6.50%→5.50%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>57→48</t>
+          <t>192→183</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,351억   ·   현금 85억(2.5%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,351억   ·   현금 43억(1.3%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1335,7 +1335,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,529억   ·   현금 77억(3.0%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 4종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,529억   ·   현금 38억(1.5%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1533,23 +1533,23 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>켐트로닉스</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-3481455186</v>
+        <v>-583350180</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>3.50%→2.15%</t>
+          <t>0.64%→0.40%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>99→60</t>
+          <t>105→66</t>
         </is>
       </c>
     </row>
@@ -1577,23 +1577,23 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>켐트로닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-583350180</v>
+        <v>-3481455186</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.40%</t>
+          <t>3.50%→2.15%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>105→66</t>
+          <t>99→60</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,921억   ·   현금 26억(1.3%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,921억   ·   현금 13억(0.7%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1921,7 +1921,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억   ·   현금 3억(1.1%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 7종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억   ·   현금 2억(0.5%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 7종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2346,7 +2346,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억   ·   현금 9억(1.8%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억   ·   현금 4억(0.9%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260917.xlsx
+++ b/reports/pdf_rolling5_20260917.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-10 ~ 2026-09-17  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-10 ~ 2026-09-17  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -816,67 +816,67 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1122371766</v>
+        <v>-1262912230</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.47%</t>
+          <t>1.09%→0.70%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>112→73</t>
+          <t>137→98</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>853152692</v>
+        <v>3457655789</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.62%→1.79%</t>
+          <t>1.09%→1.87%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>153→171</t>
+          <t>26→44</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1262912230</v>
+        <v>-1122371766</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.70%</t>
+          <t>0.79%→0.47%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>137→98</t>
+          <t>112→73</t>
         </is>
       </c>
     </row>
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3457655789</v>
+        <v>853152692</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.09%→1.87%</t>
+          <t>1.62%→1.79%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>26→44</t>
+          <t>153→171</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1533,23 +1533,23 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>켐트로닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-583350180</v>
+        <v>-3481455186</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.40%</t>
+          <t>3.50%→2.15%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>105→66</t>
+          <t>99→60</t>
         </is>
       </c>
     </row>
@@ -1577,23 +1577,23 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>켐트로닉스</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-3481455186</v>
+        <v>-583350180</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>3.50%→2.15%</t>
+          <t>0.64%→0.40%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>99→60</t>
+          <t>105→66</t>
         </is>
       </c>
     </row>
@@ -1919,492 +1919,82 @@
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억   ·   현금 2억(0.5%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 7종목  /  매도 8종목</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K48" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="20" t="n"/>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="20" t="n"/>
+      <c r="J46" s="20" t="n"/>
+      <c r="K46" s="20" t="n"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억   ·   현금 4억(0.9%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>61585965</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>0.56%→0.79%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>135→188</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-106</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-35059480</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>2.92%→2.79%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>2,452→2,346</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>선익시스템</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>191372891</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>0.34%→1.02%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>19→58</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-35419980</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>5.03%→4.91%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>869→847</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>80797454</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>1.08%→1.37%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>100→127</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-17</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-198491887</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>3.82%→3.11%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>91→74</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>30190983</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>1.82%→1.93%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>319→338</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>클래시스</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-35839980</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>0.27%→0.14%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>33→17</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>58113967</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>0.99%→1.20%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>66→80</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-15</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-53234970</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>4.29%→4.10%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>336→321</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C54" s="11" t="n">
-        <v>31940982</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>0.28%→0.40%</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>22→31</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>원익머트리얼즈</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>-29483983</v>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>2.14%→2.03%</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>262→249</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C55" s="11" t="n">
-        <v>27194984</v>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>2.87%→2.97%</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>88→91</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>-58505967</v>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>2.55%→2.35%</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>85→78</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="17" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <v>-67164962</v>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>1.84%→1.60%</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>38→33</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억   ·   현금 4억(0.9%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="20" t="n"/>
-      <c r="G61" s="20" t="n"/>
-      <c r="H61" s="20" t="n"/>
-      <c r="I61" s="20" t="n"/>
-      <c r="J61" s="20" t="n"/>
-      <c r="K61" s="20" t="n"/>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="20" t="n"/>
+      <c r="I51" s="20" t="n"/>
+      <c r="J51" s="20" t="n"/>
+      <c r="K51" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="17">
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G29:K29"/>
-    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260917.xlsx
+++ b/reports/pdf_rolling5_20260917.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-10 ~ 2026-09-17  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-10 ~ 2026-09-17  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -839,23 +839,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3457655789</v>
+        <v>853152692</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.09%→1.87%</t>
+          <t>1.62%→1.79%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>26→44</t>
+          <t>153→171</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -883,23 +883,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>8432427875</v>
+        <v>3457655789</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>4.74%→6.64%</t>
+          <t>1.09%→1.87%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>46→64</t>
+          <t>26→44</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>853152692</v>
+        <v>8432427875</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.62%→1.79%</t>
+          <t>4.74%→6.64%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>153→171</t>
+          <t>46→64</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1204,23 +1204,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2189188006</v>
+        <v>-1222521862</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>3.36%→2.58%</t>
+          <t>6.50%→5.50%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>57→48</t>
+          <t>192→183</t>
         </is>
       </c>
     </row>
@@ -1232,23 +1232,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1222521862</v>
+        <v>-2189188006</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.50%→5.50%</t>
+          <t>3.36%→2.58%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>192→183</t>
+          <t>57→48</t>
         </is>
       </c>
     </row>
@@ -1533,23 +1533,23 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>켐트로닉스</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-3481455186</v>
+        <v>-583350180</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>3.50%→2.15%</t>
+          <t>0.64%→0.40%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>99→60</t>
+          <t>105→66</t>
         </is>
       </c>
     </row>
@@ -1577,23 +1577,23 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>켐트로닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-583350180</v>
+        <v>-3481455186</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.40%</t>
+          <t>3.50%→2.15%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>105→66</t>
+          <t>99→60</t>
         </is>
       </c>
     </row>
@@ -1919,82 +1919,492 @@
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="20" t="n"/>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
-      <c r="G46" s="20" t="n"/>
-      <c r="H46" s="20" t="n"/>
-      <c r="I46" s="20" t="n"/>
-      <c r="J46" s="20" t="n"/>
-      <c r="K46" s="20" t="n"/>
-    </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억   ·   현금 2억(0.5%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 7종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>61585965</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>0.56%→0.79%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>135→188</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-106</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-35059480</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>2.92%→2.79%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>2,452→2,346</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>191372891</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>0.34%→1.02%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>19→58</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-35419980</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>5.03%→4.91%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>869→847</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>80797454</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>1.08%→1.37%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>100→127</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-198491887</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>3.82%→3.11%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>91→74</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>30190983</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>1.82%→1.93%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>319→338</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>클래시스</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-35839980</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>0.27%→0.14%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>33→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>58113967</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>0.99%→1.20%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>66→80</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-53234970</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>4.29%→4.10%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>336→321</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>31940982</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>0.28%→0.40%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>22→31</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-29483983</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>2.14%→2.03%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>262→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>27194984</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>2.87%→2.97%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>88→91</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-58505967</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>2.55%→2.35%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>85→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-67164962</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>1.84%→1.60%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>38→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억   ·   현금 4억(0.9%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
-      <c r="G51" s="20" t="n"/>
-      <c r="H51" s="20" t="n"/>
-      <c r="I51" s="20" t="n"/>
-      <c r="J51" s="20" t="n"/>
-      <c r="K51" s="20" t="n"/>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="20" t="n"/>
+      <c r="G61" s="20" t="n"/>
+      <c r="H61" s="20" t="n"/>
+      <c r="I61" s="20" t="n"/>
+      <c r="J61" s="20" t="n"/>
+      <c r="K61" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G29:K29"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="G47:K47"/>
     <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260917.xlsx
+++ b/reports/pdf_rolling5_20260917.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-10 ~ 2026-09-17  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-10 ~ 2026-09-17  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -816,67 +816,67 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1262912230</v>
+        <v>-1122371766</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.70%</t>
+          <t>0.79%→0.47%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>137→98</t>
+          <t>112→73</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>853152692</v>
+        <v>8432427875</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.62%→1.79%</t>
+          <t>4.74%→6.64%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>153→171</t>
+          <t>46→64</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1122371766</v>
+        <v>-1262912230</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.47%</t>
+          <t>1.09%→0.70%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>112→73</t>
+          <t>137→98</t>
         </is>
       </c>
     </row>
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>8432427875</v>
+        <v>853152692</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>4.74%→6.64%</t>
+          <t>1.62%→1.79%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>46→64</t>
+          <t>153→171</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1092,23 +1092,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-435435200</v>
+        <v>-773573155</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.13%→1.05%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>143→131</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1120,23 +1120,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-773573155</v>
+        <v>-435435200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.13%→1.05%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>143→131</t>
         </is>
       </c>
     </row>
@@ -1204,23 +1204,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1222521862</v>
+        <v>-2189188006</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>6.50%→5.50%</t>
+          <t>3.36%→2.58%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>192→183</t>
+          <t>57→48</t>
         </is>
       </c>
     </row>
@@ -1232,23 +1232,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2189188006</v>
+        <v>-1222521862</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.36%→2.58%</t>
+          <t>6.50%→5.50%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>57→48</t>
+          <t>192→183</t>
         </is>
       </c>
     </row>
@@ -1919,492 +1919,82 @@
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억   ·   현금 2억(0.5%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 7종목  /  매도 8종목</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K48" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="20" t="n"/>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="20" t="n"/>
+      <c r="J46" s="20" t="n"/>
+      <c r="K46" s="20" t="n"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억   ·   현금 4억(0.9%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>61585965</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>0.56%→0.79%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>135→188</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-106</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-35059480</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>2.92%→2.79%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>2,452→2,346</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>선익시스템</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>191372891</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>0.34%→1.02%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>19→58</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-35419980</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>5.03%→4.91%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>869→847</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>80797454</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>1.08%→1.37%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>100→127</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-17</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-198491887</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>3.82%→3.11%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>91→74</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>30190983</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>1.82%→1.93%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>319→338</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>클래시스</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-35839980</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>0.27%→0.14%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>33→17</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>58113967</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>0.99%→1.20%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>66→80</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-15</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-53234970</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>4.29%→4.10%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>336→321</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C54" s="11" t="n">
-        <v>31940982</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>0.28%→0.40%</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>22→31</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>원익머트리얼즈</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>-29483983</v>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>2.14%→2.03%</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>262→249</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C55" s="11" t="n">
-        <v>27194984</v>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>2.87%→2.97%</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>88→91</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>-58505967</v>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>2.55%→2.35%</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>85→78</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="17" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <v>-67164962</v>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>1.84%→1.60%</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>38→33</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억   ·   현금 4억(0.9%)      오늘 2026-09-17  vs  5일전 2026-09-10      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="20" t="n"/>
-      <c r="G61" s="20" t="n"/>
-      <c r="H61" s="20" t="n"/>
-      <c r="I61" s="20" t="n"/>
-      <c r="J61" s="20" t="n"/>
-      <c r="K61" s="20" t="n"/>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="20" t="n"/>
+      <c r="I51" s="20" t="n"/>
+      <c r="J51" s="20" t="n"/>
+      <c r="K51" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="17">
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G29:K29"/>
-    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
